--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-patient-explanation.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-patient-explanation.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Patient Right to Explanation</t>
+    <t>EU AI Patient Explanation Communication</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Documents the fulfillment of the patient's right to a clear and meaningful explanation regarding the AI's role and the clinical decision (LAW-07).</t>
+    <t>A Communication profile documenting patient-facing information about the AI-supported workflow, including the role of the AI system and the related clinical review where applicable.</t>
   </si>
   <si>
     <t>Purpose</t>
